--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2172,54 +2172,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>360891</v>
+        <v>135245545</v>
       </c>
       <c r="B16" t="n">
-        <v>80376</v>
+        <v>78823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1150</v>
+        <v>772</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangytterlav</t>
+          <t>Elfenbenslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscopannaria ahlneri</t>
+          <t>Heterodermia speciosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.M.Jørg.) P.M.Jørg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Wulfen) Trevis.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410208</v>
+        <v>410235</v>
       </c>
       <c r="R16" t="n">
-        <v>7019649</v>
+        <v>7019654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,17 +2240,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>50-60 bålar, 220 cm2 på en yta som är 1 m lång och 0,7 m hög + tre bålar 1,5 m längre österut</t>
+          <t>På tre olika ställen på olika block inom 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,39 +2269,26 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>på sluttande yta (70-80 grader) på SSO-sidan av 2 m högt och 10 m långt block</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>71291685</v>
+        <v>360891</v>
       </c>
       <c r="B17" t="n">
         <v>80376</v>
@@ -2325,22 +2316,29 @@
           <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R17" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2364,12 +2362,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50-60 bålar, 220 cm2 på en yta som är 1 m lång och 0,7 m hög + tre bålar 1,5 m längre österut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,23 +2383,37 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>på sluttande yta (70-80 grader) på SSO-sidan av 2 m högt och 10 m långt block</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79692019</v>
+        <v>71291685</v>
       </c>
       <c r="B18" t="n">
         <v>80376</v>
@@ -2425,19 +2442,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410260</v>
+        <v>410217</v>
       </c>
       <c r="R18" t="n">
-        <v>7019678</v>
+        <v>7019672</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2461,12 +2480,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,19 +2500,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95863639</v>
+        <v>79692019</v>
       </c>
       <c r="B19" t="n">
         <v>80376</v>
@@ -2524,14 +2543,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410206</v>
+        <v>410260</v>
       </c>
       <c r="R19" t="n">
-        <v>7019652</v>
+        <v>7019678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,22 +2577,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,19 +2597,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104702750</v>
+        <v>95863639</v>
       </c>
       <c r="B20" t="n">
         <v>80376</v>
@@ -2629,22 +2638,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410203</v>
+        <v>410206</v>
       </c>
       <c r="R20" t="n">
-        <v>7019666</v>
+        <v>7019652</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2668,12 +2674,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2682,26 +2698,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118272311</v>
+        <v>104702750</v>
       </c>
       <c r="B21" t="n">
         <v>80376</v>
@@ -2739,13 +2754,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410212</v>
+        <v>410203</v>
       </c>
       <c r="R21" t="n">
-        <v>7019643</v>
+        <v>7019666</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2769,17 +2784,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>vid skylten</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,22 +2805,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>368948</v>
+        <v>118272311</v>
       </c>
       <c r="B22" t="n">
-        <v>80386</v>
+        <v>80376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2818,37 +2828,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Grangytterlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Fuscopannaria ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
+          <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410240</v>
+        <v>410212</v>
       </c>
       <c r="R22" t="n">
-        <v>7019683</v>
+        <v>7019643</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,17 +2885,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
+          <t>vid skylten</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2891,34 +2904,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Blockbrant</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>377889</v>
+        <v>368948</v>
       </c>
       <c r="B23" t="n">
         <v>80386</v>
@@ -2949,14 +2954,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410244</v>
+        <v>410240</v>
       </c>
       <c r="R23" t="n">
-        <v>7019657</v>
+        <v>7019683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,12 +2988,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3000,27 +3010,31 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Blockbrant</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79692020</v>
+        <v>377889</v>
       </c>
       <c r="B24" t="n">
         <v>80386</v>
@@ -3051,14 +3065,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410260</v>
+        <v>410244</v>
       </c>
       <c r="R24" t="n">
-        <v>7019678</v>
+        <v>7019657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,12 +3099,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3101,23 +3115,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95863647</v>
+        <v>79692020</v>
       </c>
       <c r="B25" t="n">
         <v>80386</v>
@@ -3148,14 +3167,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410233</v>
+        <v>410260</v>
       </c>
       <c r="R25" t="n">
-        <v>7019663</v>
+        <v>7019678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,22 +3201,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3212,19 +3221,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104702755</v>
+        <v>95863647</v>
       </c>
       <c r="B26" t="n">
         <v>80386</v>
@@ -3253,22 +3262,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410203</v>
+        <v>410233</v>
       </c>
       <c r="R26" t="n">
-        <v>7019666</v>
+        <v>7019663</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3292,12 +3298,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3306,68 +3322,69 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104689749</v>
+        <v>104702755</v>
       </c>
       <c r="B27" t="n">
-        <v>80379</v>
+        <v>80386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410178</v>
+        <v>410203</v>
       </c>
       <c r="R27" t="n">
-        <v>7019689</v>
+        <v>7019666</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3394,76 +3411,62 @@
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På mossig sydvänd klippa</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104690042</v>
+        <v>135245554</v>
       </c>
       <c r="B28" t="n">
-        <v>80379</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,13 +3479,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410179</v>
+        <v>410235</v>
       </c>
       <c r="R28" t="n">
-        <v>7019661</v>
+        <v>7019654</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3506,19 +3509,34 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På block med elfenbenslav.</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
@@ -3527,60 +3545,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>335154</v>
+        <v>104689749</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Frey</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410190</v>
+        <v>410178</v>
       </c>
       <c r="R29" t="n">
-        <v>7019679</v>
+        <v>7019689</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3604,12 +3623,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På mossig sydvänd klippa</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3620,76 +3654,64 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104689896</v>
+        <v>104690042</v>
       </c>
       <c r="B30" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Frey</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410187</v>
+        <v>410179</v>
       </c>
       <c r="R30" t="n">
-        <v>7019668</v>
+        <v>7019661</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3719,46 +3741,37 @@
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118272291</v>
+        <v>335154</v>
       </c>
       <c r="B31" t="n">
         <v>78802</v>
@@ -3787,19 +3800,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410194</v>
+        <v>410190</v>
       </c>
       <c r="R31" t="n">
-        <v>7019673</v>
+        <v>7019679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3826,17 +3836,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,29 +3850,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>71291701</v>
+        <v>104689896</v>
       </c>
       <c r="B32" t="n">
-        <v>79486</v>
+        <v>78802</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3875,39 +3884,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Frey</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Åre, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410217</v>
+        <v>410187</v>
       </c>
       <c r="R32" t="n">
-        <v>7019672</v>
+        <v>7019668</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,12 +3948,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,57 +3978,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>903569</v>
+        <v>118272291</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1230</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Frey</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410208</v>
+        <v>410194</v>
       </c>
       <c r="R33" t="n">
-        <v>7019649</v>
+        <v>7019673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,12 +4058,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4042,55 +4077,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>71291956</v>
+        <v>71291701</v>
       </c>
       <c r="B34" t="n">
-        <v>80433</v>
+        <v>79486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4164,7 +4195,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104689754</v>
+        <v>903569</v>
       </c>
       <c r="B35" t="n">
         <v>80433</v>
@@ -4193,20 +4224,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410178</v>
+        <v>410208</v>
       </c>
       <c r="R35" t="n">
-        <v>7019689</v>
+        <v>7019649</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4230,22 +4260,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,23 +4276,28 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111054199</v>
+        <v>71291956</v>
       </c>
       <c r="B36" t="n">
         <v>80433</v>
@@ -4301,20 +4326,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410214</v>
+        <v>410217</v>
       </c>
       <c r="R36" t="n">
-        <v>7019663</v>
+        <v>7019672</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4338,22 +4364,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4368,22 +4384,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135006312</v>
+        <v>104689754</v>
       </c>
       <c r="B37" t="n">
-        <v>80489</v>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4409,19 +4425,20 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410232</v>
+        <v>410178</v>
       </c>
       <c r="R37" t="n">
-        <v>7019629</v>
+        <v>7019689</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4445,22 +4462,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4475,57 +4492,58 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>517477</v>
+        <v>111054199</v>
       </c>
       <c r="B38" t="n">
-        <v>97185</v>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410228</v>
+        <v>410214</v>
       </c>
       <c r="R38" t="n">
-        <v>7019647</v>
+        <v>7019663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,12 +4570,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4568,53 +4596,48 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>635537</v>
+        <v>135006312</v>
       </c>
       <c r="B39" t="n">
-        <v>96445</v>
+        <v>80489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2665</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4624,10 +4647,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410228</v>
+        <v>410232</v>
       </c>
       <c r="R39" t="n">
-        <v>7019647</v>
+        <v>7019629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,12 +4677,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4670,31 +4703,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95863765</v>
+        <v>517477</v>
       </c>
       <c r="B40" t="n">
-        <v>96445</v>
+        <v>97185</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,21 +4730,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2665</v>
+        <v>2420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4754,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410233</v>
+        <v>410228</v>
       </c>
       <c r="R40" t="n">
-        <v>7019663</v>
+        <v>7019647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4756,22 +4784,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4782,23 +4800,28 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118272380</v>
+        <v>635537</v>
       </c>
       <c r="B41" t="n">
         <v>96445</v>
@@ -4827,20 +4850,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410244</v>
+        <v>410228</v>
       </c>
       <c r="R41" t="n">
-        <v>7019652</v>
+        <v>7019647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4867,12 +4886,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4881,29 +4900,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>653422</v>
+        <v>95863765</v>
       </c>
       <c r="B42" t="n">
-        <v>96437</v>
+        <v>96445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,21 +4934,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4935,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410228</v>
+        <v>410233</v>
       </c>
       <c r="R42" t="n">
-        <v>7019647</v>
+        <v>7019663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,12 +4988,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4981,31 +5014,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135009615</v>
+        <v>118272380</v>
       </c>
       <c r="B43" t="n">
-        <v>92188</v>
+        <v>96445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5013,34 +5041,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3008</v>
+        <v>2665</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410188</v>
+        <v>410244</v>
       </c>
       <c r="R43" t="n">
-        <v>7019599</v>
+        <v>7019652</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,22 +5099,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5091,72 +5113,64 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1050518</v>
+        <v>653422</v>
       </c>
       <c r="B44" t="n">
-        <v>92037</v>
+        <v>96437</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3277</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410229</v>
+        <v>410228</v>
       </c>
       <c r="R44" t="n">
-        <v>7019650</v>
+        <v>7019647</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5183,12 +5197,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5202,37 +5216,28 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>på marken mellan jätteblock i rasmark</t>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150139</v>
+        <v>135009615</v>
       </c>
       <c r="B45" t="n">
-        <v>92632</v>
+        <v>92188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5240,37 +5245,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>3008</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410290</v>
+        <v>410188</v>
       </c>
       <c r="R45" t="n">
-        <v>7019688</v>
+        <v>7019599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5297,12 +5299,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5311,64 +5323,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135009619</v>
+        <v>1050518</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>92037</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410188</v>
+        <v>410229</v>
       </c>
       <c r="R46" t="n">
-        <v>7019599</v>
+        <v>7019650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,22 +5415,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,61 +5431,78 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>på marken mellan jätteblock i rasmark</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1867923</v>
+        <v>129150139</v>
       </c>
       <c r="B47" t="n">
-        <v>79413</v>
+        <v>92632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410229</v>
+        <v>410290</v>
       </c>
       <c r="R47" t="n">
-        <v>7019650</v>
+        <v>7019688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,12 +5529,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5516,67 +5543,51 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>2 substratenheter # på två block</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1870126</v>
+        <v>135009619</v>
       </c>
       <c r="B48" t="n">
-        <v>79413</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410208</v>
+        <v>410188</v>
       </c>
       <c r="R48" t="n">
-        <v>7019649</v>
+        <v>7019599</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,12 +5627,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5632,28 +5653,23 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>71291930</v>
+        <v>1867923</v>
       </c>
       <c r="B49" t="n">
         <v>79413</v>
@@ -5682,21 +5698,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410217</v>
+        <v>410229</v>
       </c>
       <c r="R49" t="n">
-        <v>7019672</v>
+        <v>7019650</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5720,12 +5734,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,61 +5750,78 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>2 substratenheter # på två block</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1897841</v>
+        <v>1870126</v>
       </c>
       <c r="B50" t="n">
-        <v>80336</v>
+        <v>79413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410244</v>
+        <v>410208</v>
       </c>
       <c r="R50" t="n">
-        <v>7019657</v>
+        <v>7019649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5854,10 +5885,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1995736</v>
+        <v>71291930</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>79413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,37 +5896,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410208</v>
+        <v>410217</v>
       </c>
       <c r="R51" t="n">
-        <v>7019649</v>
+        <v>7019672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5919,12 +5952,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5935,69 +5968,64 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>95863645</v>
+        <v>1897841</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>410233</v>
+        <v>410244</v>
       </c>
       <c r="R52" t="n">
-        <v>7019663</v>
+        <v>7019657</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6021,27 +6049,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På klippa</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,23 +6065,28 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>101373439</v>
+        <v>1995736</v>
       </c>
       <c r="B53" t="n">
         <v>80432</v>
@@ -6097,20 +6115,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>410193</v>
+        <v>410208</v>
       </c>
       <c r="R53" t="n">
-        <v>7019656</v>
+        <v>7019649</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6134,22 +6151,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6161,32 +6168,27 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101373528</v>
+        <v>95863645</v>
       </c>
       <c r="B54" t="n">
         <v>80432</v>
@@ -6215,20 +6217,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410192</v>
+        <v>410233</v>
       </c>
       <c r="R54" t="n">
-        <v>7019661</v>
+        <v>7019663</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6252,22 +6253,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6278,33 +6284,23 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101375643</v>
+        <v>101373439</v>
       </c>
       <c r="B55" t="n">
         <v>80432</v>
@@ -6340,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410198</v>
+        <v>410193</v>
       </c>
       <c r="R55" t="n">
-        <v>7019691</v>
+        <v>7019656</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
@@ -6375,7 +6371,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6385,7 +6381,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6397,19 +6393,14 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6427,7 +6418,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101376247</v>
+        <v>101373528</v>
       </c>
       <c r="B56" t="n">
         <v>80432</v>
@@ -6463,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410138</v>
+        <v>410192</v>
       </c>
       <c r="R56" t="n">
-        <v>7019682</v>
+        <v>7019661</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6498,7 +6489,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6508,7 +6499,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6520,19 +6511,14 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6550,7 +6536,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111054203</v>
+        <v>101375643</v>
       </c>
       <c r="B57" t="n">
         <v>80432</v>
@@ -6582,17 +6568,17 @@
       <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410223</v>
+        <v>410198</v>
       </c>
       <c r="R57" t="n">
-        <v>7019666</v>
+        <v>7019691</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,22 +6602,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,26 +6628,41 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135005851</v>
+        <v>101376247</v>
       </c>
       <c r="B58" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6687,19 +6688,20 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410239</v>
+        <v>410138</v>
       </c>
       <c r="R58" t="n">
-        <v>7019661</v>
+        <v>7019682</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6723,22 +6725,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6749,61 +6751,77 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2072213</v>
+        <v>111054203</v>
       </c>
       <c r="B59" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>410244</v>
+        <v>410223</v>
       </c>
       <c r="R59" t="n">
-        <v>7019657</v>
+        <v>7019666</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6830,12 +6848,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6846,53 +6874,48 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80320740</v>
+        <v>135005851</v>
       </c>
       <c r="B60" t="n">
-        <v>80467</v>
+        <v>80488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6902,10 +6925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>410257</v>
+        <v>410239</v>
       </c>
       <c r="R60" t="n">
-        <v>7019709</v>
+        <v>7019661</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6932,12 +6955,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6948,31 +6981,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>lodyta, kalksten</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Westberg, Måns Svensson</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104689756</v>
+        <v>2072213</v>
       </c>
       <c r="B61" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6980,38 +7008,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>410178</v>
+        <v>410244</v>
       </c>
       <c r="R61" t="n">
-        <v>7019689</v>
+        <v>7019657</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7035,22 +7062,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7061,26 +7078,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135006258</v>
+        <v>80320740</v>
       </c>
       <c r="B62" t="n">
-        <v>80499</v>
+        <v>80467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7112,10 +7134,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>410232</v>
+        <v>410257</v>
       </c>
       <c r="R62" t="n">
-        <v>7019629</v>
+        <v>7019709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7142,22 +7164,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7168,26 +7180,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>lodyta, kalksten</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Martin Westberg, Måns Svensson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2002484</v>
+        <v>104689756</v>
       </c>
       <c r="B63" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7195,37 +7212,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>410178</v>
       </c>
       <c r="R63" t="n">
-        <v>7019664</v>
+        <v>7019689</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7249,12 +7267,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7265,16 +7293,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7284,21 +7302,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2026706</v>
+        <v>135006258</v>
       </c>
       <c r="B64" t="n">
-        <v>80468</v>
+        <v>80499</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7306,34 +7320,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410244</v>
+        <v>410232</v>
       </c>
       <c r="R64" t="n">
-        <v>7019657</v>
+        <v>7019629</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7360,17 +7374,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>fler arter…</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7381,31 +7400,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95863642</v>
+        <v>2002484</v>
       </c>
       <c r="B65" t="n">
-        <v>58327</v>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7413,37 +7427,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410233</v>
+        <v>410178</v>
       </c>
       <c r="R65" t="n">
-        <v>7019663</v>
+        <v>7019664</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7467,22 +7481,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7493,69 +7497,78 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112503689</v>
+        <v>2026706</v>
       </c>
       <c r="B66" t="n">
-        <v>58057</v>
+        <v>80468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>410198</v>
+        <v>410244</v>
       </c>
       <c r="R66" t="n">
-        <v>7019691</v>
+        <v>7019657</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7579,22 +7592,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>fler arter…</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7605,26 +7613,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135008507</v>
+        <v>95863642</v>
       </c>
       <c r="B67" t="n">
-        <v>99099</v>
+        <v>58327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7632,51 +7645,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220093</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410192</v>
+        <v>410233</v>
       </c>
       <c r="R67" t="n">
-        <v>7019659</v>
+        <v>7019663</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7700,27 +7699,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Under överluta på stort block.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7735,65 +7729,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135005916</v>
+        <v>112503689</v>
       </c>
       <c r="B68" t="n">
-        <v>99217</v>
+        <v>58057</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410247</v>
+        <v>410198</v>
       </c>
       <c r="R68" t="n">
-        <v>7019657</v>
+        <v>7019691</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7817,22 +7811,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7847,22 +7841,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135009830</v>
+        <v>135008507</v>
       </c>
       <c r="B69" t="n">
-        <v>99001</v>
+        <v>99099</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,37 +7864,51 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223049</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410232</v>
+        <v>410192</v>
       </c>
       <c r="R69" t="n">
-        <v>7019629</v>
+        <v>7019659</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7929,7 +7937,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7939,7 +7947,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Under överluta på stort block.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7954,22 +7967,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6570236</v>
+        <v>135005916</v>
       </c>
       <c r="B70" t="n">
-        <v>80392</v>
+        <v>99217</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7977,31 +7990,36 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410244</v>
+        <v>410247</v>
       </c>
       <c r="R70" t="n">
         <v>7019657</v>
@@ -8031,12 +8049,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8047,53 +8075,48 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>95863640</v>
+        <v>135009830</v>
       </c>
       <c r="B71" t="n">
-        <v>79043</v>
+        <v>99001</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229615</v>
+        <v>223049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8103,10 +8126,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410227</v>
+        <v>410232</v>
       </c>
       <c r="R71" t="n">
-        <v>7019630</v>
+        <v>7019629</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8133,22 +8156,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,22 +8186,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71291827</v>
+        <v>6570236</v>
       </c>
       <c r="B72" t="n">
-        <v>80398</v>
+        <v>80392</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8186,39 +8209,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229748</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410217</v>
+        <v>410244</v>
       </c>
       <c r="R72" t="n">
-        <v>7019672</v>
+        <v>7019657</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8242,12 +8263,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8258,19 +8279,230 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>95863640</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>229615</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grynig kolvlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pilophorus cereolus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Hellb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>410227</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7019630</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>71291827</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>410217</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7019672</v>
+      </c>
+      <c r="S74" t="n">
+        <v>50</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Michael Tholin</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Michael Tholin</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2923,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>368948</v>
+        <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80386</v>
+        <v>80422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2934,34 +2934,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Grangytterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Fuscopannaria ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
+          <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410240</v>
+        <v>410211</v>
       </c>
       <c r="R23" t="n">
-        <v>7019683</v>
+        <v>7019654</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,17 +2988,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
+          <t>Vid skylten och provytan.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,32 +3019,23 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Blockbrant</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>377889</v>
+        <v>368948</v>
       </c>
       <c r="B24" t="n">
         <v>80386</v>
@@ -3065,14 +3066,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410244</v>
+        <v>410240</v>
       </c>
       <c r="R24" t="n">
-        <v>7019657</v>
+        <v>7019683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,12 +3100,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,27 +3122,31 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Blockbrant</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79692020</v>
+        <v>377889</v>
       </c>
       <c r="B25" t="n">
         <v>80386</v>
@@ -3167,14 +3177,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410260</v>
+        <v>410244</v>
       </c>
       <c r="R25" t="n">
-        <v>7019678</v>
+        <v>7019657</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,12 +3211,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3217,23 +3227,28 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95863647</v>
+        <v>79692020</v>
       </c>
       <c r="B26" t="n">
         <v>80386</v>
@@ -3264,14 +3279,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410233</v>
+        <v>410260</v>
       </c>
       <c r="R26" t="n">
-        <v>7019663</v>
+        <v>7019678</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,22 +3313,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,19 +3333,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104702755</v>
+        <v>95863647</v>
       </c>
       <c r="B27" t="n">
         <v>80386</v>
@@ -3369,22 +3374,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410203</v>
+        <v>410233</v>
       </c>
       <c r="R27" t="n">
-        <v>7019666</v>
+        <v>7019663</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3408,12 +3410,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,29 +3434,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135245554</v>
+        <v>104702755</v>
       </c>
       <c r="B28" t="n">
-        <v>80432</v>
+        <v>80386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,13 +3490,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410235</v>
+        <v>410203</v>
       </c>
       <c r="R28" t="n">
-        <v>7019654</v>
+        <v>7019666</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3509,27 +3520,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På block med elfenbenslav.</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,61 +3541,63 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104689749</v>
+        <v>135245554</v>
       </c>
       <c r="B29" t="n">
-        <v>80379</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410178</v>
+        <v>410235</v>
       </c>
       <c r="R29" t="n">
-        <v>7019689</v>
+        <v>7019654</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3623,27 +3621,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På mossig sydvänd klippa</t>
+          <t>På block med elfenbenslav.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3652,25 +3650,26 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104690042</v>
+        <v>104689749</v>
       </c>
       <c r="B30" t="n">
         <v>80379</v>
@@ -3699,19 +3698,17 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410179</v>
+        <v>410178</v>
       </c>
       <c r="R30" t="n">
-        <v>7019661</v>
+        <v>7019689</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3741,78 +3738,95 @@
           <t>2022-11-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På mossig sydvänd klippa</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>335154</v>
+        <v>104690042</v>
       </c>
       <c r="B31" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Frey</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410190</v>
+        <v>410179</v>
       </c>
       <c r="R31" t="n">
-        <v>7019679</v>
+        <v>7019661</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3836,44 +3850,40 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104689896</v>
+        <v>335154</v>
       </c>
       <c r="B32" t="n">
         <v>78802</v>
@@ -3901,30 +3911,20 @@
           <t>Frey</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410187</v>
+        <v>410190</v>
       </c>
       <c r="R32" t="n">
-        <v>7019668</v>
+        <v>7019679</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3948,22 +3948,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,23 +3964,28 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118272291</v>
+        <v>104689896</v>
       </c>
       <c r="B33" t="n">
         <v>78802</v>
@@ -4018,23 +4013,30 @@
           <t>Frey</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Åre, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410194</v>
+        <v>410187</v>
       </c>
       <c r="R33" t="n">
-        <v>7019673</v>
+        <v>7019668</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4058,17 +4060,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4077,29 +4084,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>71291701</v>
+        <v>118272291</v>
       </c>
       <c r="B34" t="n">
-        <v>79486</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4107,39 +4113,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Frey</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410217</v>
+        <v>410194</v>
       </c>
       <c r="R34" t="n">
-        <v>7019672</v>
+        <v>7019673</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4163,12 +4170,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,66 +4189,69 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>903569</v>
+        <v>71291701</v>
       </c>
       <c r="B35" t="n">
-        <v>80433</v>
+        <v>79486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410208</v>
+        <v>410217</v>
       </c>
       <c r="R35" t="n">
-        <v>7019649</v>
+        <v>7019672</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4260,12 +4275,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,28 +4291,23 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>71291956</v>
+        <v>903569</v>
       </c>
       <c r="B36" t="n">
         <v>80433</v>
@@ -4326,21 +4336,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R36" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4364,12 +4372,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,23 +4388,28 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104689754</v>
+        <v>71291956</v>
       </c>
       <c r="B37" t="n">
         <v>80433</v>
@@ -4425,20 +4438,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410178</v>
+        <v>410217</v>
       </c>
       <c r="R37" t="n">
-        <v>7019689</v>
+        <v>7019672</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4462,22 +4476,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,19 +4496,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111054199</v>
+        <v>104689754</v>
       </c>
       <c r="B38" t="n">
         <v>80433</v>
@@ -4536,17 +4540,17 @@
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410214</v>
+        <v>410178</v>
       </c>
       <c r="R38" t="n">
-        <v>7019663</v>
+        <v>7019689</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4570,22 +4574,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4600,22 +4604,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135006312</v>
+        <v>111054199</v>
       </c>
       <c r="B39" t="n">
-        <v>80489</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,16 +4645,17 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410232</v>
+        <v>410214</v>
       </c>
       <c r="R39" t="n">
-        <v>7019629</v>
+        <v>7019663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,22 +4682,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4707,44 +4712,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>517477</v>
+        <v>135006312</v>
       </c>
       <c r="B40" t="n">
-        <v>97185</v>
+        <v>80489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4754,10 +4759,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410228</v>
+        <v>410232</v>
       </c>
       <c r="R40" t="n">
-        <v>7019647</v>
+        <v>7019629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,12 +4789,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,31 +4815,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>635537</v>
+        <v>517477</v>
       </c>
       <c r="B41" t="n">
-        <v>96445</v>
+        <v>97185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4832,21 +4842,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2665</v>
+        <v>2420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4923,7 +4933,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95863765</v>
+        <v>635537</v>
       </c>
       <c r="B42" t="n">
         <v>96445</v>
@@ -4958,10 +4968,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410233</v>
+        <v>410228</v>
       </c>
       <c r="R42" t="n">
-        <v>7019663</v>
+        <v>7019647</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,22 +4998,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,23 +5014,28 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118272380</v>
+        <v>95863765</v>
       </c>
       <c r="B43" t="n">
         <v>96445</v>
@@ -5059,20 +5064,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410244</v>
+        <v>410233</v>
       </c>
       <c r="R43" t="n">
-        <v>7019652</v>
+        <v>7019663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5099,12 +5100,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5113,29 +5124,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>653422</v>
+        <v>118272380</v>
       </c>
       <c r="B44" t="n">
-        <v>96437</v>
+        <v>96445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5143,34 +5153,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410228</v>
+        <v>410244</v>
       </c>
       <c r="R44" t="n">
-        <v>7019647</v>
+        <v>7019652</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,12 +5211,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5211,33 +5225,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135009615</v>
+        <v>653422</v>
       </c>
       <c r="B45" t="n">
-        <v>92188</v>
+        <v>96437</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5245,21 +5255,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3008</v>
+        <v>2667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5269,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410188</v>
+        <v>410228</v>
       </c>
       <c r="R45" t="n">
-        <v>7019599</v>
+        <v>7019647</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5299,22 +5309,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5325,70 +5325,66 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1050518</v>
+        <v>135009615</v>
       </c>
       <c r="B46" t="n">
-        <v>92037</v>
+        <v>92188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3277</v>
+        <v>3008</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410229</v>
+        <v>410188</v>
       </c>
       <c r="R46" t="n">
-        <v>7019650</v>
+        <v>7019599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5415,12 +5411,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5431,78 +5437,70 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>på marken mellan jätteblock i rasmark</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150139</v>
+        <v>1050518</v>
       </c>
       <c r="B47" t="n">
-        <v>92632</v>
+        <v>92037</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>3277</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410290</v>
+        <v>410229</v>
       </c>
       <c r="R47" t="n">
-        <v>7019688</v>
+        <v>7019650</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,12 +5527,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5543,64 +5541,80 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>på marken mellan jätteblock i rasmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135009619</v>
+        <v>129150139</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>92632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410188</v>
+        <v>410290</v>
       </c>
       <c r="R48" t="n">
-        <v>7019599</v>
+        <v>7019688</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,22 +5641,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5651,63 +5655,64 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1867923</v>
+        <v>135009619</v>
       </c>
       <c r="B49" t="n">
-        <v>79413</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410229</v>
+        <v>410188</v>
       </c>
       <c r="R49" t="n">
-        <v>7019650</v>
+        <v>7019599</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5734,12 +5739,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5750,40 +5765,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AN49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>2 substratenheter # på två block</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1870126</v>
+        <v>1867923</v>
       </c>
       <c r="B50" t="n">
         <v>79413</v>
@@ -5814,14 +5812,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410208</v>
+        <v>410229</v>
       </c>
       <c r="R50" t="n">
-        <v>7019649</v>
+        <v>7019650</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5848,12 +5846,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5867,25 +5865,37 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>2 substratenheter # på två block</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>71291930</v>
+        <v>1870126</v>
       </c>
       <c r="B51" t="n">
         <v>79413</v>
@@ -5914,21 +5924,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R51" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5952,12 +5960,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,64 +5976,71 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1897841</v>
+        <v>71291930</v>
       </c>
       <c r="B52" t="n">
-        <v>80336</v>
+        <v>79413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6450</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>410244</v>
+        <v>410217</v>
       </c>
       <c r="R52" t="n">
-        <v>7019657</v>
+        <v>7019672</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6049,12 +6064,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6065,66 +6080,61 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1995736</v>
+        <v>1897841</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>410208</v>
+        <v>410244</v>
       </c>
       <c r="R53" t="n">
-        <v>7019649</v>
+        <v>7019657</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6188,7 +6198,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>95863645</v>
+        <v>1995736</v>
       </c>
       <c r="B54" t="n">
         <v>80432</v>
@@ -6223,13 +6233,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410233</v>
+        <v>410208</v>
       </c>
       <c r="R54" t="n">
-        <v>7019663</v>
+        <v>7019649</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6253,27 +6263,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På klippa</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,23 +6279,28 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101373439</v>
+        <v>95863645</v>
       </c>
       <c r="B55" t="n">
         <v>80432</v>
@@ -6329,20 +6329,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410193</v>
+        <v>410233</v>
       </c>
       <c r="R55" t="n">
-        <v>7019656</v>
+        <v>7019663</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6366,22 +6365,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6392,33 +6396,23 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101373528</v>
+        <v>101373439</v>
       </c>
       <c r="B56" t="n">
         <v>80432</v>
@@ -6454,10 +6448,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410192</v>
+        <v>410193</v>
       </c>
       <c r="R56" t="n">
-        <v>7019661</v>
+        <v>7019656</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6489,7 +6483,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6499,7 +6493,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6536,7 +6530,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101375643</v>
+        <v>101373528</v>
       </c>
       <c r="B57" t="n">
         <v>80432</v>
@@ -6572,10 +6566,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410198</v>
+        <v>410192</v>
       </c>
       <c r="R57" t="n">
-        <v>7019691</v>
+        <v>7019661</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -6607,7 +6601,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6617,7 +6611,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6629,19 +6623,14 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6659,7 +6648,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101376247</v>
+        <v>101375643</v>
       </c>
       <c r="B58" t="n">
         <v>80432</v>
@@ -6695,10 +6684,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410138</v>
+        <v>410198</v>
       </c>
       <c r="R58" t="n">
-        <v>7019682</v>
+        <v>7019691</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -6730,7 +6719,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6740,7 +6729,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6754,17 +6743,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6782,7 +6771,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111054203</v>
+        <v>101376247</v>
       </c>
       <c r="B59" t="n">
         <v>80432</v>
@@ -6814,17 +6803,17 @@
       <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>410223</v>
+        <v>410138</v>
       </c>
       <c r="R59" t="n">
-        <v>7019666</v>
+        <v>7019682</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,22 +6837,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6874,26 +6863,41 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135005851</v>
+        <v>111054203</v>
       </c>
       <c r="B60" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6919,16 +6923,17 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>410239</v>
+        <v>410223</v>
       </c>
       <c r="R60" t="n">
-        <v>7019661</v>
+        <v>7019666</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6955,22 +6960,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6985,57 +6990,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2072213</v>
+        <v>135005851</v>
       </c>
       <c r="B61" t="n">
-        <v>80461</v>
+        <v>80488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>410244</v>
+        <v>410239</v>
       </c>
       <c r="R61" t="n">
-        <v>7019657</v>
+        <v>7019661</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7062,12 +7067,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7078,31 +7093,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>80320740</v>
+        <v>2072213</v>
       </c>
       <c r="B62" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7110,34 +7120,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>410257</v>
+        <v>410244</v>
       </c>
       <c r="R62" t="n">
-        <v>7019709</v>
+        <v>7019657</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7164,12 +7174,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7181,27 +7191,27 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>lodyta, kalksten</t>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Westberg, Måns Svensson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104689756</v>
+        <v>80320740</v>
       </c>
       <c r="B63" t="n">
         <v>80467</v>
@@ -7230,20 +7240,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>410178</v>
+        <v>410257</v>
       </c>
       <c r="R63" t="n">
-        <v>7019689</v>
+        <v>7019709</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7267,22 +7276,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7293,26 +7292,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>lodyta, kalksten</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Martin Westberg, Måns Svensson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135006258</v>
+        <v>104689756</v>
       </c>
       <c r="B64" t="n">
-        <v>80499</v>
+        <v>80467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7338,19 +7342,20 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410232</v>
+        <v>410178</v>
       </c>
       <c r="R64" t="n">
-        <v>7019629</v>
+        <v>7019689</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7374,22 +7379,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7404,22 +7409,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002484</v>
+        <v>135006258</v>
       </c>
       <c r="B65" t="n">
-        <v>80468</v>
+        <v>80499</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7427,34 +7432,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410178</v>
+        <v>410232</v>
       </c>
       <c r="R65" t="n">
-        <v>7019664</v>
+        <v>7019629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7481,12 +7486,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7497,37 +7512,23 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2026706</v>
+        <v>2002484</v>
       </c>
       <c r="B66" t="n">
         <v>80468</v>
@@ -7558,14 +7559,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>410244</v>
+        <v>410178</v>
       </c>
       <c r="R66" t="n">
-        <v>7019657</v>
+        <v>7019664</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7592,17 +7593,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>fler arter…</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7616,28 +7612,37 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>95863642</v>
+        <v>2026706</v>
       </c>
       <c r="B67" t="n">
-        <v>58327</v>
+        <v>80468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7645,37 +7650,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410233</v>
+        <v>410244</v>
       </c>
       <c r="R67" t="n">
-        <v>7019663</v>
+        <v>7019657</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7699,22 +7704,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>fler arter…</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7725,43 +7725,48 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112503689</v>
+        <v>95863642</v>
       </c>
       <c r="B68" t="n">
-        <v>58057</v>
+        <v>58327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7769,25 +7774,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410198</v>
+        <v>410233</v>
       </c>
       <c r="R68" t="n">
-        <v>7019691</v>
+        <v>7019663</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7811,22 +7811,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7841,74 +7841,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135008507</v>
+        <v>112503689</v>
       </c>
       <c r="B69" t="n">
-        <v>99099</v>
+        <v>58057</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220093</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410192</v>
+        <v>410198</v>
       </c>
       <c r="R69" t="n">
-        <v>7019659</v>
+        <v>7019691</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7932,27 +7923,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Under överluta på stort block.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7967,22 +7953,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135005916</v>
+        <v>135008507</v>
       </c>
       <c r="B70" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7990,24 +7976,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -8019,13 +8014,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410247</v>
+        <v>410192</v>
       </c>
       <c r="R70" t="n">
-        <v>7019657</v>
+        <v>7019659</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8054,7 +8049,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8064,7 +8059,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Under överluta på stort block.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8079,22 +8079,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135009830</v>
+        <v>135005916</v>
       </c>
       <c r="B71" t="n">
-        <v>99001</v>
+        <v>99217</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8102,34 +8102,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410232</v>
+        <v>410247</v>
       </c>
       <c r="R71" t="n">
-        <v>7019629</v>
+        <v>7019657</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,7 +8166,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8171,7 +8176,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8198,10 +8203,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6570236</v>
+        <v>135009830</v>
       </c>
       <c r="B72" t="n">
-        <v>80392</v>
+        <v>99001</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8209,34 +8214,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>223049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410244</v>
+        <v>410232</v>
       </c>
       <c r="R72" t="n">
-        <v>7019657</v>
+        <v>7019629</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8263,12 +8268,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8279,66 +8294,61 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95863640</v>
+        <v>6570236</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>80392</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410227</v>
+        <v>410244</v>
       </c>
       <c r="R73" t="n">
-        <v>7019630</v>
+        <v>7019657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,22 +8375,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8391,66 +8391,69 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>71291827</v>
+        <v>95863640</v>
       </c>
       <c r="B74" t="n">
-        <v>80398</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229748</v>
+        <v>229615</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410217</v>
+        <v>410227</v>
       </c>
       <c r="R74" t="n">
-        <v>7019672</v>
+        <v>7019630</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8474,12 +8477,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8494,15 +8507,114 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>71291827</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>410217</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7019672</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
           <t>Michael Tholin</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>Michael Tholin</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/268874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/268875</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/269805</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/269806</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/271900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79692018</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863636</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104724</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104702753</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111054242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272236</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135245545</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,6 +2490,11 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/360891</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291685</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2606,6 +2696,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79692019</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2713,6 +2808,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863639</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104702750</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272311</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3032,6 +3142,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135007524</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3143,6 +3258,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/368948</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/377889</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3342,6 +3467,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79692020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3449,6 +3579,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863647</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3550,6 +3685,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104702755</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3666,6 +3806,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135245554</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3779,6 +3924,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104689749</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3880,6 +4030,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104690042</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3982,6 +4137,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/335154</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4099,6 +4259,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104689896</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272291</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291701</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4406,6 +4581,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/903569</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4505,6 +4685,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291956</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4613,6 +4798,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104689754</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4721,6 +4911,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111054199</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4824,10 +5019,15 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135006312</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4930,6 +5130,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/517477</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5032,6 +5237,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/635537</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5139,6 +5349,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863765</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5241,6 +5456,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272380</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5343,6 +5563,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/653422</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5450,6 +5675,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009615</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5568,6 +5798,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1050518</t>
         </is>
       </c>
     </row>
@@ -5671,6 +5906,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150139</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5778,6 +6018,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009619</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5892,6 +6137,11 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1867923</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5994,6 +6244,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1870126</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6093,6 +6348,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291930</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6195,6 +6455,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1897841</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6297,6 +6562,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1995736</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6409,6 +6679,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863645</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6527,6 +6802,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101373439</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6645,6 +6925,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101373528</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6768,6 +7053,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101375643</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6891,6 +7181,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101376247</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6999,6 +7294,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111054203</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7106,6 +7406,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135005851</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7208,6 +7513,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072213</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7310,6 +7620,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80320740</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7418,6 +7733,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104689756</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7521,10 +7841,15 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135006258</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7636,6 +7961,11 @@
           <t>Elfenbenslav 2008</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2002484</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7743,6 +8073,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2026706</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7850,6 +8185,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863642</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7962,6 +8302,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112503689</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8088,6 +8433,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135008507</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8200,6 +8550,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135005916</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8307,6 +8662,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135009830</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8409,6 +8769,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6570236</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8516,6 +8881,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863640</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8615,8 +8985,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -2250,7 +2250,7 @@
         <v>135245545</v>
       </c>
       <c r="B16" t="n">
-        <v>78823</v>
+        <v>78861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80422</v>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135245554</v>
       </c>
       <c r="B29" t="n">
-        <v>80432</v>
+        <v>80470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>135006312</v>
       </c>
       <c r="B40" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>135009615</v>
       </c>
       <c r="B46" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135009619</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135005851</v>
       </c>
       <c r="B61" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>135006258</v>
       </c>
       <c r="B65" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>135008507</v>
       </c>
       <c r="B70" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>135005916</v>
       </c>
       <c r="B71" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>135009830</v>
       </c>
       <c r="B72" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -2250,7 +2250,7 @@
         <v>135245545</v>
       </c>
       <c r="B16" t="n">
-        <v>78861</v>
+        <v>78888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80460</v>
+        <v>80487</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135245554</v>
       </c>
       <c r="B29" t="n">
-        <v>80470</v>
+        <v>80497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>135006312</v>
       </c>
       <c r="B40" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>135009615</v>
       </c>
       <c r="B46" t="n">
-        <v>92230</v>
+        <v>92257</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135009619</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>135005851</v>
       </c>
       <c r="B61" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>135006258</v>
       </c>
       <c r="B65" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>135008507</v>
       </c>
       <c r="B70" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>135005916</v>
       </c>
       <c r="B71" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
         <v>135009830</v>
       </c>
       <c r="B72" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,54 +2247,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>360891</v>
+        <v>135245545</v>
       </c>
       <c r="B16" t="n">
-        <v>80376</v>
+        <v>78891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1150</v>
+        <v>772</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangytterlav</t>
+          <t>Elfenbenslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscopannaria ahlneri</t>
+          <t>Heterodermia speciosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.M.Jørg.) P.M.Jørg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Wulfen) Trevis.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410208</v>
+        <v>410235</v>
       </c>
       <c r="R16" t="n">
-        <v>7019649</v>
+        <v>7019654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,17 +2315,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>50-60 bålar, 220 cm2 på en yta som är 1 m lång och 0,7 m hög + tre bålar 1,5 m längre österut</t>
+          <t>På tre olika ställen på olika block inom 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,44 +2344,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>på sluttande yta (70-80 grader) på SSO-sidan av 2 m högt och 10 m långt block</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/360891</t>
+          <t>https://artportalen.se/Sighting/135245545</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>71291685</v>
+        <v>360891</v>
       </c>
       <c r="B17" t="n">
         <v>80376</v>
@@ -2405,22 +2396,29 @@
           <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R17" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2444,12 +2442,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50-60 bålar, 220 cm2 på en yta som är 1 m lång och 0,7 m hög + tre bålar 1,5 m längre österut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,28 +2463,42 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>på sluttande yta (70-80 grader) på SSO-sidan av 2 m högt och 10 m långt block</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291685</t>
+          <t>https://artportalen.se/Sighting/360891</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79692019</v>
+        <v>71291685</v>
       </c>
       <c r="B18" t="n">
         <v>80376</v>
@@ -2510,19 +2527,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410260</v>
+        <v>410217</v>
       </c>
       <c r="R18" t="n">
-        <v>7019678</v>
+        <v>7019672</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,12 +2565,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,24 +2585,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79692019</t>
+          <t>https://artportalen.se/Sighting/71291685</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95863639</v>
+        <v>79692019</v>
       </c>
       <c r="B19" t="n">
         <v>80376</v>
@@ -2614,14 +2633,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410206</v>
+        <v>410260</v>
       </c>
       <c r="R19" t="n">
-        <v>7019652</v>
+        <v>7019678</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,22 +2667,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,24 +2687,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863639</t>
+          <t>https://artportalen.se/Sighting/79692019</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104702750</v>
+        <v>95863639</v>
       </c>
       <c r="B20" t="n">
         <v>80376</v>
@@ -2724,22 +2733,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410203</v>
+        <v>410206</v>
       </c>
       <c r="R20" t="n">
-        <v>7019666</v>
+        <v>7019652</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,12 +2769,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2777,31 +2793,30 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104702750</t>
+          <t>https://artportalen.se/Sighting/95863639</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118272311</v>
+        <v>104702750</v>
       </c>
       <c r="B21" t="n">
         <v>80376</v>
@@ -2839,13 +2854,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410212</v>
+        <v>410203</v>
       </c>
       <c r="R21" t="n">
-        <v>7019643</v>
+        <v>7019666</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,17 +2884,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>vid skylten</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,27 +2905,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118272311</t>
+          <t>https://artportalen.se/Sighting/104702750</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>368948</v>
+        <v>118272311</v>
       </c>
       <c r="B22" t="n">
-        <v>80386</v>
+        <v>80376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,37 +2933,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Grangytterlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Fuscopannaria ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
+          <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410240</v>
+        <v>410212</v>
       </c>
       <c r="R22" t="n">
-        <v>7019683</v>
+        <v>7019643</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2977,17 +2990,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
+          <t>vid skylten</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,39 +3009,31 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Blockbrant</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/368948</t>
+          <t>https://artportalen.se/Sighting/118272311</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>377889</v>
+        <v>368948</v>
       </c>
       <c r="B23" t="n">
         <v>80386</v>
@@ -3059,14 +3064,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410244</v>
+        <v>410240</v>
       </c>
       <c r="R23" t="n">
-        <v>7019657</v>
+        <v>7019683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,12 +3098,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,32 +3120,36 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Blockbrant</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/377889</t>
+          <t>https://artportalen.se/Sighting/368948</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79692020</v>
+        <v>377889</v>
       </c>
       <c r="B24" t="n">
         <v>80386</v>
@@ -3166,14 +3180,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410260</v>
+        <v>410244</v>
       </c>
       <c r="R24" t="n">
-        <v>7019678</v>
+        <v>7019657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3200,12 +3214,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,28 +3230,33 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79692020</t>
+          <t>https://artportalen.se/Sighting/377889</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95863647</v>
+        <v>79692020</v>
       </c>
       <c r="B25" t="n">
         <v>80386</v>
@@ -3268,14 +3287,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410233</v>
+        <v>410260</v>
       </c>
       <c r="R25" t="n">
-        <v>7019663</v>
+        <v>7019678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3302,22 +3321,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,24 +3341,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863647</t>
+          <t>https://artportalen.se/Sighting/79692020</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104702755</v>
+        <v>95863647</v>
       </c>
       <c r="B26" t="n">
         <v>80386</v>
@@ -3378,22 +3387,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410203</v>
+        <v>410233</v>
       </c>
       <c r="R26" t="n">
-        <v>7019666</v>
+        <v>7019663</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3417,12 +3423,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,73 +3447,74 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104702755</t>
+          <t>https://artportalen.se/Sighting/95863647</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104689749</v>
+        <v>104702755</v>
       </c>
       <c r="B27" t="n">
-        <v>80379</v>
+        <v>80386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410178</v>
+        <v>410203</v>
       </c>
       <c r="R27" t="n">
-        <v>7019689</v>
+        <v>7019666</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3524,81 +3541,67 @@
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På mossig sydvänd klippa</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689749</t>
+          <t>https://artportalen.se/Sighting/104702755</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104690042</v>
+        <v>135245554</v>
       </c>
       <c r="B28" t="n">
-        <v>80379</v>
+        <v>80500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3611,13 +3614,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410179</v>
+        <v>410235</v>
       </c>
       <c r="R28" t="n">
-        <v>7019661</v>
+        <v>7019654</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,19 +3644,34 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På block med elfenbenslav.</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
@@ -3662,65 +3680,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104690042</t>
+          <t>https://artportalen.se/Sighting/135245554</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>335154</v>
+        <v>104689749</v>
       </c>
       <c r="B29" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Frey</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410190</v>
+        <v>410178</v>
       </c>
       <c r="R29" t="n">
-        <v>7019679</v>
+        <v>7019689</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3744,12 +3763,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På mossig sydvänd klippa</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,81 +3794,69 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/335154</t>
+          <t>https://artportalen.se/Sighting/104689749</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104689896</v>
+        <v>104690042</v>
       </c>
       <c r="B30" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Frey</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410187</v>
+        <v>410179</v>
       </c>
       <c r="R30" t="n">
-        <v>7019668</v>
+        <v>7019661</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3864,51 +3886,42 @@
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689896</t>
+          <t>https://artportalen.se/Sighting/104690042</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118272291</v>
+        <v>335154</v>
       </c>
       <c r="B31" t="n">
         <v>78802</v>
@@ -3937,19 +3950,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410194</v>
+        <v>410190</v>
       </c>
       <c r="R31" t="n">
-        <v>7019673</v>
+        <v>7019679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,17 +3986,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3995,34 +4000,38 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118272291</t>
+          <t>https://artportalen.se/Sighting/335154</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>71291701</v>
+        <v>104689896</v>
       </c>
       <c r="B32" t="n">
-        <v>79486</v>
+        <v>78802</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,39 +4039,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Frey</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Åre, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410217</v>
+        <v>410187</v>
       </c>
       <c r="R32" t="n">
-        <v>7019672</v>
+        <v>7019668</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4086,12 +4103,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4106,62 +4133,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291701</t>
+          <t>https://artportalen.se/Sighting/104689896</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>903569</v>
+        <v>118272291</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1230</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Frey</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410208</v>
+        <v>410194</v>
       </c>
       <c r="R33" t="n">
-        <v>7019649</v>
+        <v>7019673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4188,12 +4218,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,60 +4237,56 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/903569</t>
+          <t>https://artportalen.se/Sighting/118272291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>71291956</v>
+        <v>71291701</v>
       </c>
       <c r="B34" t="n">
-        <v>80433</v>
+        <v>79486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4328,13 +4359,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291956</t>
+          <t>https://artportalen.se/Sighting/71291701</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104689754</v>
+        <v>903569</v>
       </c>
       <c r="B35" t="n">
         <v>80433</v>
@@ -4363,20 +4394,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410178</v>
+        <v>410208</v>
       </c>
       <c r="R35" t="n">
-        <v>7019689</v>
+        <v>7019649</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4400,22 +4430,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4426,28 +4446,33 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689754</t>
+          <t>https://artportalen.se/Sighting/903569</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111054199</v>
+        <v>71291956</v>
       </c>
       <c r="B36" t="n">
         <v>80433</v>
@@ -4476,20 +4501,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410214</v>
+        <v>410217</v>
       </c>
       <c r="R36" t="n">
-        <v>7019663</v>
+        <v>7019672</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4513,22 +4539,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4543,27 +4559,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111054199</t>
+          <t>https://artportalen.se/Sighting/71291956</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135006312</v>
+        <v>104689754</v>
       </c>
       <c r="B37" t="n">
-        <v>80554</v>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4589,19 +4605,20 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410232</v>
+        <v>410178</v>
       </c>
       <c r="R37" t="n">
-        <v>7019629</v>
+        <v>7019689</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4625,22 +4642,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4655,62 +4672,63 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135006312</t>
+          <t>https://artportalen.se/Sighting/104689754</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>517477</v>
+        <v>111054199</v>
       </c>
       <c r="B38" t="n">
-        <v>97185</v>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410228</v>
+        <v>410214</v>
       </c>
       <c r="R38" t="n">
-        <v>7019647</v>
+        <v>7019663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,12 +4755,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4753,58 +4781,53 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/517477</t>
+          <t>https://artportalen.se/Sighting/111054199</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>635537</v>
+        <v>135006312</v>
       </c>
       <c r="B39" t="n">
-        <v>96445</v>
+        <v>80554</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2665</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4837,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410228</v>
+        <v>410232</v>
       </c>
       <c r="R39" t="n">
-        <v>7019647</v>
+        <v>7019629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,12 +4867,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4860,36 +4893,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/635537</t>
+          <t>https://artportalen.se/Sighting/135006312</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95863765</v>
+        <v>517477</v>
       </c>
       <c r="B40" t="n">
-        <v>96445</v>
+        <v>97185</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,21 +4925,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2665</v>
+        <v>2420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4949,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410233</v>
+        <v>410228</v>
       </c>
       <c r="R40" t="n">
-        <v>7019663</v>
+        <v>7019647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4951,22 +4979,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,28 +4995,33 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863765</t>
+          <t>https://artportalen.se/Sighting/517477</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118272380</v>
+        <v>635537</v>
       </c>
       <c r="B41" t="n">
         <v>96445</v>
@@ -5027,20 +5050,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>410244</v>
+        <v>410228</v>
       </c>
       <c r="R41" t="n">
-        <v>7019652</v>
+        <v>7019647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,12 +5086,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,34 +5100,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118272380</t>
+          <t>https://artportalen.se/Sighting/635537</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>653422</v>
+        <v>95863765</v>
       </c>
       <c r="B42" t="n">
-        <v>96437</v>
+        <v>96445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,21 +5139,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5140,10 +5163,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410228</v>
+        <v>410233</v>
       </c>
       <c r="R42" t="n">
-        <v>7019647</v>
+        <v>7019663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5170,12 +5193,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,36 +5219,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/653422</t>
+          <t>https://artportalen.se/Sighting/95863765</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135009615</v>
+        <v>118272380</v>
       </c>
       <c r="B43" t="n">
-        <v>92257</v>
+        <v>96445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,34 +5251,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3008</v>
+        <v>2665</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410188</v>
+        <v>410244</v>
       </c>
       <c r="R43" t="n">
-        <v>7019599</v>
+        <v>7019652</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5277,22 +5309,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,77 +5323,69 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009615</t>
+          <t>https://artportalen.se/Sighting/118272380</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1050518</v>
+        <v>653422</v>
       </c>
       <c r="B44" t="n">
-        <v>92037</v>
+        <v>96437</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3277</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410229</v>
+        <v>410228</v>
       </c>
       <c r="R44" t="n">
-        <v>7019650</v>
+        <v>7019647</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5398,12 +5412,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,42 +5431,33 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>på marken mellan jätteblock i rasmark</t>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1050518</t>
+          <t>https://artportalen.se/Sighting/653422</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150139</v>
+        <v>135009615</v>
       </c>
       <c r="B45" t="n">
-        <v>92632</v>
+        <v>92257</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5460,37 +5465,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>3008</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410290</v>
+        <v>410188</v>
       </c>
       <c r="R45" t="n">
-        <v>7019688</v>
+        <v>7019599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5517,12 +5519,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5531,69 +5543,77 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150139</t>
+          <t>https://artportalen.se/Sighting/135009615</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135009619</v>
+        <v>1050518</v>
       </c>
       <c r="B46" t="n">
-        <v>79438</v>
+        <v>92037</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410188</v>
+        <v>410229</v>
       </c>
       <c r="R46" t="n">
-        <v>7019599</v>
+        <v>7019650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5620,22 +5640,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5646,66 +5656,83 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>på marken mellan jätteblock i rasmark</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009619</t>
+          <t>https://artportalen.se/Sighting/1050518</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1867923</v>
+        <v>129150139</v>
       </c>
       <c r="B47" t="n">
-        <v>79413</v>
+        <v>92632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410229</v>
+        <v>410290</v>
       </c>
       <c r="R47" t="n">
-        <v>7019650</v>
+        <v>7019688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5732,12 +5759,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,72 +5773,56 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>2 substratenheter # på två block</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1867923</t>
+          <t>https://artportalen.se/Sighting/129150139</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1870126</v>
+        <v>135009619</v>
       </c>
       <c r="B48" t="n">
-        <v>79413</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5821,10 +5832,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410208</v>
+        <v>410188</v>
       </c>
       <c r="R48" t="n">
-        <v>7019649</v>
+        <v>7019599</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5851,12 +5862,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5867,33 +5888,28 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1870126</t>
+          <t>https://artportalen.se/Sighting/135009619</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>71291930</v>
+        <v>1867923</v>
       </c>
       <c r="B49" t="n">
         <v>79413</v>
@@ -5922,21 +5938,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410217</v>
+        <v>410229</v>
       </c>
       <c r="R49" t="n">
-        <v>7019672</v>
+        <v>7019650</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5960,12 +5974,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5976,66 +5990,83 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>2 substratenheter # på två block</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291930</t>
+          <t>https://artportalen.se/Sighting/1867923</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1897841</v>
+        <v>1870126</v>
       </c>
       <c r="B50" t="n">
-        <v>80336</v>
+        <v>79413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410244</v>
+        <v>410208</v>
       </c>
       <c r="R50" t="n">
-        <v>7019657</v>
+        <v>7019649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6098,16 +6129,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1897841</t>
+          <t>https://artportalen.se/Sighting/1870126</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1995736</v>
+        <v>71291930</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>79413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,37 +6146,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410208</v>
+        <v>410217</v>
       </c>
       <c r="R51" t="n">
-        <v>7019649</v>
+        <v>7019672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6169,12 +6202,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6185,74 +6218,69 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1995736</t>
+          <t>https://artportalen.se/Sighting/71291930</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>95863645</v>
+        <v>1897841</v>
       </c>
       <c r="B52" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>410233</v>
+        <v>410244</v>
       </c>
       <c r="R52" t="n">
-        <v>7019663</v>
+        <v>7019657</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6276,27 +6304,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På klippa</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6307,28 +6320,33 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863645</t>
+          <t>https://artportalen.se/Sighting/1897841</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>101373439</v>
+        <v>1995736</v>
       </c>
       <c r="B53" t="n">
         <v>80432</v>
@@ -6357,20 +6375,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>410193</v>
+        <v>410208</v>
       </c>
       <c r="R53" t="n">
-        <v>7019656</v>
+        <v>7019649</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6394,22 +6411,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6421,37 +6428,32 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101373439</t>
+          <t>https://artportalen.se/Sighting/1995736</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101373528</v>
+        <v>95863645</v>
       </c>
       <c r="B54" t="n">
         <v>80432</v>
@@ -6480,20 +6482,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410192</v>
+        <v>410233</v>
       </c>
       <c r="R54" t="n">
-        <v>7019661</v>
+        <v>7019663</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6517,22 +6518,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6543,38 +6549,28 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101373528</t>
+          <t>https://artportalen.se/Sighting/95863645</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101375643</v>
+        <v>101373439</v>
       </c>
       <c r="B55" t="n">
         <v>80432</v>
@@ -6610,10 +6606,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410198</v>
+        <v>410193</v>
       </c>
       <c r="R55" t="n">
-        <v>7019691</v>
+        <v>7019656</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
@@ -6645,7 +6641,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6655,7 +6651,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6667,19 +6663,14 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6696,13 +6687,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101375643</t>
+          <t>https://artportalen.se/Sighting/101373439</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101376247</v>
+        <v>101373528</v>
       </c>
       <c r="B56" t="n">
         <v>80432</v>
@@ -6738,10 +6729,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410138</v>
+        <v>410192</v>
       </c>
       <c r="R56" t="n">
-        <v>7019682</v>
+        <v>7019661</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6773,7 +6764,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6783,7 +6774,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6795,19 +6786,14 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6824,13 +6810,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101376247</t>
+          <t>https://artportalen.se/Sighting/101373528</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111054203</v>
+        <v>101375643</v>
       </c>
       <c r="B57" t="n">
         <v>80432</v>
@@ -6862,17 +6848,17 @@
       <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410223</v>
+        <v>410198</v>
       </c>
       <c r="R57" t="n">
-        <v>7019666</v>
+        <v>7019691</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6896,22 +6882,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6922,31 +6908,46 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111054203</t>
+          <t>https://artportalen.se/Sighting/101375643</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135005851</v>
+        <v>101376247</v>
       </c>
       <c r="B58" t="n">
-        <v>80553</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6972,19 +6973,20 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410239</v>
+        <v>410138</v>
       </c>
       <c r="R58" t="n">
-        <v>7019661</v>
+        <v>7019682</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7008,22 +7010,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7034,66 +7036,82 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135005851</t>
+          <t>https://artportalen.se/Sighting/101376247</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2072213</v>
+        <v>111054203</v>
       </c>
       <c r="B59" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>410244</v>
+        <v>410223</v>
       </c>
       <c r="R59" t="n">
-        <v>7019657</v>
+        <v>7019666</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7120,12 +7138,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7136,58 +7164,53 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2072213</t>
+          <t>https://artportalen.se/Sighting/111054203</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80320740</v>
+        <v>135005851</v>
       </c>
       <c r="B60" t="n">
-        <v>80467</v>
+        <v>80553</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7197,10 +7220,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>410257</v>
+        <v>410239</v>
       </c>
       <c r="R60" t="n">
-        <v>7019709</v>
+        <v>7019661</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7227,12 +7250,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7243,36 +7276,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>lodyta, kalksten</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Westberg, Måns Svensson</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80320740</t>
+          <t>https://artportalen.se/Sighting/135005851</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104689756</v>
+        <v>2072213</v>
       </c>
       <c r="B61" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7280,38 +7308,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>410178</v>
+        <v>410244</v>
       </c>
       <c r="R61" t="n">
-        <v>7019689</v>
+        <v>7019657</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7335,22 +7362,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7361,31 +7378,36 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689756</t>
+          <t>https://artportalen.se/Sighting/2072213</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135006258</v>
+        <v>80320740</v>
       </c>
       <c r="B62" t="n">
-        <v>80564</v>
+        <v>80467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7417,10 +7439,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>410232</v>
+        <v>410257</v>
       </c>
       <c r="R62" t="n">
-        <v>7019629</v>
+        <v>7019709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7447,22 +7469,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7473,31 +7485,36 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>lodyta, kalksten</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Martin Westberg, Måns Svensson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135006258</t>
+          <t>https://artportalen.se/Sighting/80320740</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2002484</v>
+        <v>104689756</v>
       </c>
       <c r="B63" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7505,37 +7522,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>410178</v>
       </c>
       <c r="R63" t="n">
-        <v>7019664</v>
+        <v>7019689</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7559,12 +7577,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7575,16 +7603,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7594,26 +7612,22 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2002484</t>
+          <t>https://artportalen.se/Sighting/104689756</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2026706</v>
+        <v>135006258</v>
       </c>
       <c r="B64" t="n">
-        <v>80468</v>
+        <v>80564</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7621,34 +7635,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410244</v>
+        <v>410232</v>
       </c>
       <c r="R64" t="n">
-        <v>7019657</v>
+        <v>7019629</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7675,17 +7689,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>fler arter…</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7696,36 +7715,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2026706</t>
+          <t>https://artportalen.se/Sighting/135006258</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95863642</v>
+        <v>2002484</v>
       </c>
       <c r="B65" t="n">
-        <v>58327</v>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7733,37 +7747,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410233</v>
+        <v>410178</v>
       </c>
       <c r="R65" t="n">
-        <v>7019663</v>
+        <v>7019664</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7787,22 +7801,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7813,74 +7817,83 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863642</t>
+          <t>https://artportalen.se/Sighting/2002484</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112503689</v>
+        <v>2026706</v>
       </c>
       <c r="B66" t="n">
-        <v>58057</v>
+        <v>80468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>410198</v>
+        <v>410244</v>
       </c>
       <c r="R66" t="n">
-        <v>7019691</v>
+        <v>7019657</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7904,22 +7917,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>fler arter…</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7930,31 +7938,36 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112503689</t>
+          <t>https://artportalen.se/Sighting/2026706</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135008507</v>
+        <v>95863642</v>
       </c>
       <c r="B67" t="n">
-        <v>99173</v>
+        <v>58327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7962,51 +7975,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220093</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410192</v>
+        <v>410233</v>
       </c>
       <c r="R67" t="n">
-        <v>7019659</v>
+        <v>7019663</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8030,27 +8029,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Under överluta på stort block.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8065,70 +8059,70 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135008507</t>
+          <t>https://artportalen.se/Sighting/95863642</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135005916</v>
+        <v>112503689</v>
       </c>
       <c r="B68" t="n">
-        <v>99291</v>
+        <v>58057</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410247</v>
+        <v>410198</v>
       </c>
       <c r="R68" t="n">
-        <v>7019657</v>
+        <v>7019691</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8152,22 +8146,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8182,27 +8176,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135005916</t>
+          <t>https://artportalen.se/Sighting/112503689</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135009830</v>
+        <v>135008507</v>
       </c>
       <c r="B69" t="n">
-        <v>99075</v>
+        <v>99173</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8210,37 +8204,51 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223049</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410232</v>
+        <v>410192</v>
       </c>
       <c r="R69" t="n">
-        <v>7019629</v>
+        <v>7019659</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8269,7 +8277,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8279,7 +8287,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Under överluta på stort block.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8294,27 +8307,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009830</t>
+          <t>https://artportalen.se/Sighting/135008507</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6570236</v>
+        <v>135005916</v>
       </c>
       <c r="B70" t="n">
-        <v>80392</v>
+        <v>99291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,31 +8335,36 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410244</v>
+        <v>410247</v>
       </c>
       <c r="R70" t="n">
         <v>7019657</v>
@@ -8376,12 +8394,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8392,58 +8420,53 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6570236</t>
+          <t>https://artportalen.se/Sighting/135005916</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>95863640</v>
+        <v>135009830</v>
       </c>
       <c r="B71" t="n">
-        <v>79043</v>
+        <v>99075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229615</v>
+        <v>223049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8453,10 +8476,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410227</v>
+        <v>410232</v>
       </c>
       <c r="R71" t="n">
-        <v>7019630</v>
+        <v>7019629</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8483,22 +8506,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8513,27 +8536,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863640</t>
+          <t>https://artportalen.se/Sighting/135009830</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71291827</v>
+        <v>6570236</v>
       </c>
       <c r="B72" t="n">
-        <v>80398</v>
+        <v>80392</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8541,39 +8564,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229748</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410217</v>
+        <v>410244</v>
       </c>
       <c r="R72" t="n">
-        <v>7019672</v>
+        <v>7019657</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8597,12 +8618,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8613,20 +8634,241 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6570236</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>95863640</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>229615</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grynig kolvlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pilophorus cereolus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Hellb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>410227</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7019630</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863640</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>71291827</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>410217</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7019672</v>
+      </c>
+      <c r="S74" t="n">
+        <v>50</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Michael Tholin</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Michael Tholin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/71291827</t>
         </is>
@@ -8705,6 +8947,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ74"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>368948</v>
+        <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80386</v>
+        <v>80490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,34 +3044,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Grangytterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Fuscopannaria ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
+          <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410240</v>
+        <v>410211</v>
       </c>
       <c r="R23" t="n">
-        <v>7019683</v>
+        <v>7019654</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3098,17 +3098,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
+          <t>Vid skylten och provytan.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,37 +3129,28 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Blockbrant</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Uno Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/368948</t>
+          <t>https://artportalen.se/Sighting/135007524</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>377889</v>
+        <v>368948</v>
       </c>
       <c r="B24" t="n">
         <v>80386</v>
@@ -3180,14 +3181,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets Obrant, 3 km SV om Undersåker,, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410244</v>
+        <v>410240</v>
       </c>
       <c r="R24" t="n">
-        <v>7019657</v>
+        <v>7019683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,12 +3215,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2002-04-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sparsam på överluta och snedluta på mycket stort block (10x20 m) i nederdelen av ostvänd blockbrant, kantad av äldre granskog (&gt;100 år).</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,32 +3237,36 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Blockbrant</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/377889</t>
+          <t>https://artportalen.se/Sighting/368948</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79692020</v>
+        <v>377889</v>
       </c>
       <c r="B25" t="n">
         <v>80386</v>
@@ -3287,14 +3297,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410260</v>
+        <v>410244</v>
       </c>
       <c r="R25" t="n">
-        <v>7019678</v>
+        <v>7019657</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,12 +3331,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,28 +3347,33 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79692020</t>
+          <t>https://artportalen.se/Sighting/377889</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95863647</v>
+        <v>79692020</v>
       </c>
       <c r="B26" t="n">
         <v>80386</v>
@@ -3389,14 +3404,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Undersåker, Välaberget (strax SV om Henåvallen)., Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410233</v>
+        <v>410260</v>
       </c>
       <c r="R26" t="n">
-        <v>7019663</v>
+        <v>7019678</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,22 +3438,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,24 +3458,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863647</t>
+          <t>https://artportalen.se/Sighting/79692020</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104702755</v>
+        <v>95863647</v>
       </c>
       <c r="B27" t="n">
         <v>80386</v>
@@ -3499,22 +3504,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410203</v>
+        <v>410233</v>
       </c>
       <c r="R27" t="n">
-        <v>7019666</v>
+        <v>7019663</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3538,12 +3540,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3552,34 +3564,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104702755</t>
+          <t>https://artportalen.se/Sighting/95863647</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135245554</v>
+        <v>104702755</v>
       </c>
       <c r="B28" t="n">
-        <v>80500</v>
+        <v>80386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,13 +3625,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410235</v>
+        <v>410203</v>
       </c>
       <c r="R28" t="n">
-        <v>7019654</v>
+        <v>7019666</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3644,27 +3655,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På block med elfenbenslav.</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,66 +3676,68 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135245554</t>
+          <t>https://artportalen.se/Sighting/104702755</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104689749</v>
+        <v>135245554</v>
       </c>
       <c r="B29" t="n">
-        <v>80379</v>
+        <v>80500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410178</v>
+        <v>410235</v>
       </c>
       <c r="R29" t="n">
-        <v>7019689</v>
+        <v>7019654</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3763,27 +3761,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På mossig sydvänd klippa</t>
+          <t>På block med elfenbenslav.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,30 +3790,31 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689749</t>
+          <t>https://artportalen.se/Sighting/135245554</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104690042</v>
+        <v>104689749</v>
       </c>
       <c r="B30" t="n">
         <v>80379</v>
@@ -3844,19 +3843,17 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410179</v>
+        <v>410178</v>
       </c>
       <c r="R30" t="n">
-        <v>7019661</v>
+        <v>7019689</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3886,83 +3883,100 @@
           <t>2022-11-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-11-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På mossig sydvänd klippa</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104690042</t>
+          <t>https://artportalen.se/Sighting/104689749</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>335154</v>
+        <v>104690042</v>
       </c>
       <c r="B31" t="n">
-        <v>78802</v>
+        <v>80379</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1230</v>
+        <v>1153</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pudrad rosettlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Physcia magnussonii</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Frey</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410190</v>
+        <v>410179</v>
       </c>
       <c r="R31" t="n">
-        <v>7019679</v>
+        <v>7019661</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3986,49 +4000,45 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/335154</t>
+          <t>https://artportalen.se/Sighting/104690042</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104689896</v>
+        <v>335154</v>
       </c>
       <c r="B32" t="n">
         <v>78802</v>
@@ -4056,30 +4066,20 @@
           <t>Frey</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410187</v>
+        <v>410190</v>
       </c>
       <c r="R32" t="n">
-        <v>7019668</v>
+        <v>7019679</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4103,22 +4103,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4129,28 +4119,33 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689896</t>
+          <t>https://artportalen.se/Sighting/335154</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118272291</v>
+        <v>104689896</v>
       </c>
       <c r="B33" t="n">
         <v>78802</v>
@@ -4178,23 +4173,30 @@
           <t>Frey</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Åre, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410194</v>
+        <v>410187</v>
       </c>
       <c r="R33" t="n">
-        <v>7019673</v>
+        <v>7019668</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4218,17 +4220,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4237,34 +4244,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118272291</t>
+          <t>https://artportalen.se/Sighting/104689896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>71291701</v>
+        <v>118272291</v>
       </c>
       <c r="B34" t="n">
-        <v>79486</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4272,39 +4278,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Pudrad rosettlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Physcia magnussonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Frey</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410217</v>
+        <v>410194</v>
       </c>
       <c r="R34" t="n">
-        <v>7019672</v>
+        <v>7019673</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,12 +4335,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,71 +4354,74 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291701</t>
+          <t>https://artportalen.se/Sighting/118272291</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>903569</v>
+        <v>71291701</v>
       </c>
       <c r="B35" t="n">
-        <v>80433</v>
+        <v>79486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410208</v>
+        <v>410217</v>
       </c>
       <c r="R35" t="n">
-        <v>7019649</v>
+        <v>7019672</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4430,12 +4445,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4446,33 +4461,28 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/903569</t>
+          <t>https://artportalen.se/Sighting/71291701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>71291956</v>
+        <v>903569</v>
       </c>
       <c r="B36" t="n">
         <v>80433</v>
@@ -4501,21 +4511,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R36" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4539,12 +4547,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,28 +4563,33 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291956</t>
+          <t>https://artportalen.se/Sighting/903569</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104689754</v>
+        <v>71291956</v>
       </c>
       <c r="B37" t="n">
         <v>80433</v>
@@ -4605,20 +4618,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410178</v>
+        <v>410217</v>
       </c>
       <c r="R37" t="n">
-        <v>7019689</v>
+        <v>7019672</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,22 +4656,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4672,24 +4676,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689754</t>
+          <t>https://artportalen.se/Sighting/71291956</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111054199</v>
+        <v>104689754</v>
       </c>
       <c r="B38" t="n">
         <v>80433</v>
@@ -4721,17 +4725,17 @@
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410214</v>
+        <v>410178</v>
       </c>
       <c r="R38" t="n">
-        <v>7019663</v>
+        <v>7019689</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4755,22 +4759,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4785,27 +4789,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111054199</t>
+          <t>https://artportalen.se/Sighting/104689754</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135006312</v>
+        <v>111054199</v>
       </c>
       <c r="B39" t="n">
-        <v>80554</v>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4831,16 +4835,17 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410232</v>
+        <v>410214</v>
       </c>
       <c r="R39" t="n">
-        <v>7019629</v>
+        <v>7019663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4867,22 +4872,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4897,49 +4902,49 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135006312</t>
+          <t>https://artportalen.se/Sighting/111054199</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>517477</v>
+        <v>135006312</v>
       </c>
       <c r="B40" t="n">
-        <v>97185</v>
+        <v>80554</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2420</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogstimmia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Timmia austriaca</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410228</v>
+        <v>410232</v>
       </c>
       <c r="R40" t="n">
-        <v>7019647</v>
+        <v>7019629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4979,12 +4984,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4995,36 +5010,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/517477</t>
+          <t>https://artportalen.se/Sighting/135006312</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>635537</v>
+        <v>517477</v>
       </c>
       <c r="B41" t="n">
-        <v>96445</v>
+        <v>97185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5032,21 +5042,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2665</v>
+        <v>2420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Skogstimmia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Timmia austriaca</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5122,13 +5132,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/635537</t>
+          <t>https://artportalen.se/Sighting/517477</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95863765</v>
+        <v>635537</v>
       </c>
       <c r="B42" t="n">
         <v>96445</v>
@@ -5163,10 +5173,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410233</v>
+        <v>410228</v>
       </c>
       <c r="R42" t="n">
-        <v>7019663</v>
+        <v>7019647</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5193,22 +5203,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5219,28 +5219,33 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863765</t>
+          <t>https://artportalen.se/Sighting/635537</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118272380</v>
+        <v>95863765</v>
       </c>
       <c r="B43" t="n">
         <v>96445</v>
@@ -5269,20 +5274,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410244</v>
+        <v>410233</v>
       </c>
       <c r="R43" t="n">
-        <v>7019652</v>
+        <v>7019663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5309,12 +5310,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5323,34 +5334,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Anna Pielach, Peter Carlsson, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118272380</t>
+          <t>https://artportalen.se/Sighting/95863765</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>653422</v>
+        <v>118272380</v>
       </c>
       <c r="B44" t="n">
-        <v>96437</v>
+        <v>96445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5358,34 +5368,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410228</v>
+        <v>410244</v>
       </c>
       <c r="R44" t="n">
-        <v>7019647</v>
+        <v>7019652</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5412,12 +5426,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5426,38 +5440,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/653422</t>
+          <t>https://artportalen.se/Sighting/118272380</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135009615</v>
+        <v>653422</v>
       </c>
       <c r="B45" t="n">
-        <v>92257</v>
+        <v>96437</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5465,21 +5475,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3008</v>
+        <v>2667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5489,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>410188</v>
+        <v>410228</v>
       </c>
       <c r="R45" t="n">
-        <v>7019599</v>
+        <v>7019647</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5519,22 +5529,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,75 +5545,71 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009615</t>
+          <t>https://artportalen.se/Sighting/653422</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1050518</v>
+        <v>135009615</v>
       </c>
       <c r="B46" t="n">
-        <v>92037</v>
+        <v>92257</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3277</v>
+        <v>3008</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410229</v>
+        <v>410188</v>
       </c>
       <c r="R46" t="n">
-        <v>7019650</v>
+        <v>7019599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,12 +5636,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5656,83 +5662,75 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>på marken mellan jätteblock i rasmark</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1050518</t>
+          <t>https://artportalen.se/Sighting/135009615</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150139</v>
+        <v>1050518</v>
       </c>
       <c r="B47" t="n">
-        <v>92632</v>
+        <v>92037</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>3277</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410290</v>
+        <v>410229</v>
       </c>
       <c r="R47" t="n">
-        <v>7019688</v>
+        <v>7019650</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5759,12 +5757,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5773,69 +5771,85 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>på marken mellan jätteblock i rasmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150139</t>
+          <t>https://artportalen.se/Sighting/1050518</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135009619</v>
+        <v>129150139</v>
       </c>
       <c r="B48" t="n">
-        <v>79438</v>
+        <v>92632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Snödskallen, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>410188</v>
+        <v>410290</v>
       </c>
       <c r="R48" t="n">
-        <v>7019599</v>
+        <v>7019688</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5862,22 +5876,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5886,68 +5890,69 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009619</t>
+          <t>https://artportalen.se/Sighting/129150139</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1867923</v>
+        <v>135009619</v>
       </c>
       <c r="B49" t="n">
-        <v>79413</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>410229</v>
+        <v>410188</v>
       </c>
       <c r="R49" t="n">
-        <v>7019650</v>
+        <v>7019599</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5974,12 +5979,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5990,45 +6005,28 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AN49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>2 substratenheter # på två block</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1867923</t>
+          <t>https://artportalen.se/Sighting/135009619</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1870126</v>
+        <v>1867923</v>
       </c>
       <c r="B50" t="n">
         <v>79413</v>
@@ -6059,14 +6057,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>410208</v>
+        <v>410229</v>
       </c>
       <c r="R50" t="n">
-        <v>7019649</v>
+        <v>7019650</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6093,12 +6091,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6112,30 +6110,42 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+          <t>i nedre delen av rasmark nedanför S-vänt stup med 120-150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>2 substratenheter # på två block</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1870126</t>
+          <t>https://artportalen.se/Sighting/1867923</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>71291930</v>
+        <v>1870126</v>
       </c>
       <c r="B51" t="n">
         <v>79413</v>
@@ -6164,21 +6174,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>410217</v>
+        <v>410208</v>
       </c>
       <c r="R51" t="n">
-        <v>7019672</v>
+        <v>7019649</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6202,12 +6210,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6218,69 +6226,76 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71291930</t>
+          <t>https://artportalen.se/Sighting/1870126</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1897841</v>
+        <v>71291930</v>
       </c>
       <c r="B52" t="n">
-        <v>80336</v>
+        <v>79413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6450</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>410244</v>
+        <v>410217</v>
       </c>
       <c r="R52" t="n">
-        <v>7019657</v>
+        <v>7019672</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6304,12 +6319,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6320,71 +6335,66 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1897841</t>
+          <t>https://artportalen.se/Sighting/71291930</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1995736</v>
+        <v>1897841</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>410208</v>
+        <v>410244</v>
       </c>
       <c r="R53" t="n">
-        <v>7019649</v>
+        <v>7019657</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6447,13 +6457,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1995736</t>
+          <t>https://artportalen.se/Sighting/1897841</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>95863645</v>
+        <v>1995736</v>
       </c>
       <c r="B54" t="n">
         <v>80432</v>
@@ -6488,13 +6498,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410233</v>
+        <v>410208</v>
       </c>
       <c r="R54" t="n">
-        <v>7019663</v>
+        <v>7019649</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6518,27 +6528,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På klippa</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,28 +6544,33 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863645</t>
+          <t>https://artportalen.se/Sighting/1995736</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101373439</v>
+        <v>95863645</v>
       </c>
       <c r="B55" t="n">
         <v>80432</v>
@@ -6599,20 +6599,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410193</v>
+        <v>410233</v>
       </c>
       <c r="R55" t="n">
-        <v>7019656</v>
+        <v>7019663</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6636,22 +6635,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På klippa</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6662,38 +6666,28 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101373439</t>
+          <t>https://artportalen.se/Sighting/95863645</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101373528</v>
+        <v>101373439</v>
       </c>
       <c r="B56" t="n">
         <v>80432</v>
@@ -6729,10 +6723,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>410192</v>
+        <v>410193</v>
       </c>
       <c r="R56" t="n">
-        <v>7019661</v>
+        <v>7019656</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6764,7 +6758,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6774,7 +6768,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,13 +6804,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101373528</t>
+          <t>https://artportalen.se/Sighting/101373439</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101375643</v>
+        <v>101373528</v>
       </c>
       <c r="B57" t="n">
         <v>80432</v>
@@ -6852,10 +6846,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410198</v>
+        <v>410192</v>
       </c>
       <c r="R57" t="n">
-        <v>7019691</v>
+        <v>7019661</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
@@ -6887,7 +6881,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6897,7 +6891,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6909,19 +6903,14 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6938,13 +6927,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101375643</t>
+          <t>https://artportalen.se/Sighting/101373528</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101376247</v>
+        <v>101375643</v>
       </c>
       <c r="B58" t="n">
         <v>80432</v>
@@ -6980,10 +6969,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410138</v>
+        <v>410198</v>
       </c>
       <c r="R58" t="n">
-        <v>7019682</v>
+        <v>7019691</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -7015,7 +7004,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7025,7 +7014,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,17 +7028,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7066,13 +7055,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101376247</t>
+          <t>https://artportalen.se/Sighting/101375643</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111054203</v>
+        <v>101376247</v>
       </c>
       <c r="B59" t="n">
         <v>80432</v>
@@ -7104,17 +7093,17 @@
       <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Välaberget, Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>410223</v>
+        <v>410138</v>
       </c>
       <c r="R59" t="n">
-        <v>7019666</v>
+        <v>7019682</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7138,22 +7127,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7164,31 +7153,46 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111054203</t>
+          <t>https://artportalen.se/Sighting/101376247</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135005851</v>
+        <v>111054203</v>
       </c>
       <c r="B60" t="n">
-        <v>80553</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7214,16 +7218,17 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>410239</v>
+        <v>410223</v>
       </c>
       <c r="R60" t="n">
-        <v>7019661</v>
+        <v>7019666</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7250,22 +7255,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7280,62 +7285,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135005851</t>
+          <t>https://artportalen.se/Sighting/111054203</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2072213</v>
+        <v>135005851</v>
       </c>
       <c r="B61" t="n">
-        <v>80461</v>
+        <v>80553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>410244</v>
+        <v>410239</v>
       </c>
       <c r="R61" t="n">
-        <v>7019657</v>
+        <v>7019661</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7362,12 +7367,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7378,36 +7393,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2072213</t>
+          <t>https://artportalen.se/Sighting/135005851</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>80320740</v>
+        <v>2072213</v>
       </c>
       <c r="B62" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7415,34 +7425,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>410257</v>
+        <v>410244</v>
       </c>
       <c r="R62" t="n">
-        <v>7019709</v>
+        <v>7019657</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7469,12 +7479,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7486,32 +7496,32 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>lodyta, kalksten</t>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Westberg, Måns Svensson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80320740</t>
+          <t>https://artportalen.se/Sighting/2072213</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104689756</v>
+        <v>80320740</v>
       </c>
       <c r="B63" t="n">
         <v>80467</v>
@@ -7540,20 +7550,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Välaberget, Undersåker , Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>410178</v>
+        <v>410257</v>
       </c>
       <c r="R63" t="n">
-        <v>7019689</v>
+        <v>7019709</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7577,22 +7586,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7603,31 +7602,36 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>lodyta, kalksten</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Martin Westberg, Måns Svensson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104689756</t>
+          <t>https://artportalen.se/Sighting/80320740</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135006258</v>
+        <v>104689756</v>
       </c>
       <c r="B64" t="n">
-        <v>80564</v>
+        <v>80467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7653,19 +7657,20 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, Undersåker , Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410232</v>
+        <v>410178</v>
       </c>
       <c r="R64" t="n">
-        <v>7019629</v>
+        <v>7019689</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7689,22 +7694,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7719,27 +7724,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135006258</t>
+          <t>https://artportalen.se/Sighting/104689756</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002484</v>
+        <v>135006258</v>
       </c>
       <c r="B65" t="n">
-        <v>80468</v>
+        <v>80564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7747,34 +7752,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410178</v>
+        <v>410232</v>
       </c>
       <c r="R65" t="n">
-        <v>7019664</v>
+        <v>7019629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7801,12 +7806,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7817,42 +7832,28 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Elfenbenslav 2008</t>
-        </is>
-      </c>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2002484</t>
+          <t>https://artportalen.se/Sighting/135006258</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2026706</v>
+        <v>2002484</v>
       </c>
       <c r="B66" t="n">
         <v>80468</v>
@@ -7883,14 +7884,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välabergets sydostbrant, 9,5 km SV om Undersåkers kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>410244</v>
+        <v>410178</v>
       </c>
       <c r="R66" t="n">
-        <v>7019657</v>
+        <v>7019664</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7917,17 +7918,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>fler arter…</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7941,33 +7937,42 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
+          <t>i rasmark nedanför sydstup med 150-årig granskog</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>på 70 grader lutande O-vänd yta på knappt m-högt block</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Elfenbenslav 2008</t>
+        </is>
+      </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2026706</t>
+          <t>https://artportalen.se/Sighting/2002484</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>95863642</v>
+        <v>2026706</v>
       </c>
       <c r="B67" t="n">
-        <v>58327</v>
+        <v>80468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7975,37 +7980,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410233</v>
+        <v>410244</v>
       </c>
       <c r="R67" t="n">
-        <v>7019663</v>
+        <v>7019657</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8029,22 +8034,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>fler arter…</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8055,48 +8055,53 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863642</t>
+          <t>https://artportalen.se/Sighting/2026706</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112503689</v>
+        <v>95863642</v>
       </c>
       <c r="B68" t="n">
-        <v>58057</v>
+        <v>58327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8104,25 +8109,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Väla, Åre, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410198</v>
+        <v>410233</v>
       </c>
       <c r="R68" t="n">
-        <v>7019691</v>
+        <v>7019663</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8146,22 +8146,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8176,79 +8176,70 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112503689</t>
+          <t>https://artportalen.se/Sighting/95863642</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135008507</v>
+        <v>112503689</v>
       </c>
       <c r="B69" t="n">
-        <v>99173</v>
+        <v>58057</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220093</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Väla, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410192</v>
+        <v>410198</v>
       </c>
       <c r="R69" t="n">
-        <v>7019659</v>
+        <v>7019691</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8272,27 +8263,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Under överluta på stort block.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8307,27 +8293,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Möller Skog</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135008507</t>
+          <t>https://artportalen.se/Sighting/112503689</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135005916</v>
+        <v>135008507</v>
       </c>
       <c r="B70" t="n">
-        <v>99291</v>
+        <v>99173</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8335,24 +8321,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -8364,13 +8359,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410247</v>
+        <v>410192</v>
       </c>
       <c r="R70" t="n">
-        <v>7019657</v>
+        <v>7019659</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8399,7 +8394,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8409,7 +8404,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Under överluta på stort block.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8424,27 +8424,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog, Uno Skog</t>
+          <t>Uno Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135005916</t>
+          <t>https://artportalen.se/Sighting/135008507</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135009830</v>
+        <v>135005916</v>
       </c>
       <c r="B71" t="n">
-        <v>99075</v>
+        <v>99291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,34 +8452,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410232</v>
+        <v>410247</v>
       </c>
       <c r="R71" t="n">
-        <v>7019629</v>
+        <v>7019657</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8511,7 +8516,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8521,7 +8526,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8547,16 +8552,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135009830</t>
+          <t>https://artportalen.se/Sighting/135005916</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6570236</v>
+        <v>135009830</v>
       </c>
       <c r="B72" t="n">
-        <v>80392</v>
+        <v>99075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,34 +8569,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>223049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Välaberget, NO-vänd klippa, Jmt</t>
+          <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410244</v>
+        <v>410232</v>
       </c>
       <c r="R72" t="n">
-        <v>7019657</v>
+        <v>7019629</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8618,12 +8623,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2012-09-12</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8634,71 +8649,66 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Skogklädd bergbrant med rika klippor</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sofia Möller Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6570236</t>
+          <t>https://artportalen.se/Sighting/135009830</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95863640</v>
+        <v>6570236</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>80392</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229615</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grynig kolvlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pilophorus cereolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Välaberget, Jmt</t>
+          <t>Välaberget, NO-vänd klippa, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410227</v>
+        <v>410244</v>
       </c>
       <c r="R73" t="n">
-        <v>7019630</v>
+        <v>7019657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,22 +8735,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2012-09-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8751,71 +8751,74 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Skogklädd bergbrant med rika klippor</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95863640</t>
+          <t>https://artportalen.se/Sighting/6570236</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>71291827</v>
+        <v>95863640</v>
       </c>
       <c r="B74" t="n">
-        <v>80398</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229748</v>
+        <v>229615</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Grynig kolvlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pilophorus cereolus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Välaberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410217</v>
+        <v>410227</v>
       </c>
       <c r="R74" t="n">
-        <v>7019672</v>
+        <v>7019630</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8839,12 +8842,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8859,16 +8872,120 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Ulf Gärdenfors, Åke Berg, Niklas Hjort, Karin Wiklund, Staffan Carlsson, Urban Gunnarsson, Olle Holst, Per Darell, Tomas Troschke, Mats Williamson, Carl-Axel Andersson, Crister Albinsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95863640</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>71291827</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Välaberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>410217</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7019672</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2018-05-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Michael Tholin</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Michael Tholin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/71291827</t>
         </is>
@@ -8949,6 +9066,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80490</v>
+        <v>80492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80492</v>
+        <v>80493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80493</v>
+        <v>80494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80494</v>
+        <v>80498</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80498</v>
+        <v>80499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80499</v>
+        <v>80503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80503</v>
+        <v>80509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80509</v>
+        <v>80522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28022-2026 artfynd.xlsx
+++ b/artfynd/A 28022-2026 artfynd.xlsx
@@ -3036,7 +3036,7 @@
         <v>135007524</v>
       </c>
       <c r="B23" t="n">
-        <v>80522</v>
+        <v>80523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
